--- a/results/cot_inference/mgsm/tiny-aya-water/summary_majority.xlsx
+++ b/results/cot_inference/mgsm/tiny-aya-water/summary_majority.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="all_parse_failures" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,116 +460,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="D2" t="n">
         <v>250</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>lang</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>q_idx</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>run</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>question</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>expected</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>cot_tail</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>227</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>詹姆斯正在数他的宝可梦卡牌。他有 30 张火系、20 张草系和 40 张水系。如果他丢失了 8 张水系且购买了 14 张草系，一张随机选择的卡牌为水系的几率是多少（四舍五入到最接近的整数）？</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>33</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>要解决这个问题，我们需要确定詹姆斯手中的卡牌总数以及他手中 remaining 卡牌中 namespace  namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>zh</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>227</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>詹姆斯正在数他的宝可梦卡牌。他有 30 张火系、20 张草系和 40 张水系。如果他丢失了 8 张水系且购买了 14 张草系，一张随机选择的卡牌为水系的几率是多少（四舍五入到最接近的整数）？</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>33</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>要解决这个问题，我们需要确定詹姆斯手中的卡牌总数以及他手中 remaining 卡牌中 namespace  namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace namespace</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/results/cot_inference/mgsm/tiny-aya-water/summary_majority.xlsx
+++ b/results/cot_inference/mgsm/tiny-aya-water/summary_majority.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,26 +451,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>bn</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="D2" t="n">
         <v>250</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>156</v>
+      </c>
+      <c r="D3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>62.4%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>188</v>
+      </c>
+      <c r="D4" t="n">
+        <v>250</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>75.2%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Swahili</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sw</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>152</v>
+      </c>
+      <c r="D5" t="n">
+        <v>250</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>60.8%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>te</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>139</v>
+      </c>
+      <c r="D6" t="n">
+        <v>250</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
       </c>
     </row>
